--- a/data/Terre di Pedemonte/cost/cost_report.xlsx
+++ b/data/Terre di Pedemonte/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>482.7070075445002</v>
+        <v>396.4572605434739</v>
       </c>
       <c r="C2" t="n">
-        <v>10845.52972036053</v>
+        <v>10755.67461499293</v>
       </c>
       <c r="D2" t="n">
-        <v>3082.127095426627</v>
+        <v>4984.279579995256</v>
       </c>
       <c r="E2" t="n">
-        <v>2877.802672841075</v>
+        <v>2923.623634004434</v>
       </c>
       <c r="F2" t="n">
-        <v>22600.21283199476</v>
+        <v>20479.84408348018</v>
       </c>
       <c r="G2" t="n">
-        <v>39888.37932816749</v>
+        <v>39539.87917301628</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1066680121226813</v>
+        <v>0.1057360660421301</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>483.9037846261102</v>
+        <v>395.8931333198214</v>
       </c>
       <c r="C3" t="n">
-        <v>9038.576938303368</v>
+        <v>10725.70803580216</v>
       </c>
       <c r="D3" t="n">
-        <v>14432.75202369868</v>
+        <v>5430.07302007218</v>
       </c>
       <c r="E3" t="n">
-        <v>2708.563606847479</v>
+        <v>3058.746356935721</v>
       </c>
       <c r="F3" t="n">
-        <v>17979.25642670272</v>
+        <v>21133.53637727667</v>
       </c>
       <c r="G3" t="n">
-        <v>44643.05278017835</v>
+        <v>40743.95692340656</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1193827820371446</v>
+        <v>0.1089559657281668</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>483.0166986036054</v>
+        <v>391.7582175500826</v>
       </c>
       <c r="C4" t="n">
-        <v>10804.059539672</v>
+        <v>8900.58508579145</v>
       </c>
       <c r="D4" t="n">
-        <v>3515.614049711591</v>
+        <v>17798.66211733785</v>
       </c>
       <c r="E4" t="n">
-        <v>2952.75432207097</v>
+        <v>1831.345425619131</v>
       </c>
       <c r="F4" t="n">
-        <v>23290.8264865516</v>
+        <v>15602.71197294159</v>
       </c>
       <c r="G4" t="n">
-        <v>41046.27109660977</v>
+        <v>44525.0628192401</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1097644029832078</v>
+        <v>0.1190672576965799</v>
       </c>
     </row>
     <row r="5">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>483.8669651313664</v>
+        <v>392.6278309636343</v>
       </c>
       <c r="C5" t="n">
-        <v>9008.953003969946</v>
+        <v>8883.136917675445</v>
       </c>
       <c r="D5" t="n">
-        <v>14928.02440350619</v>
+        <v>18201.72188620616</v>
       </c>
       <c r="E5" t="n">
-        <v>2763.739160404162</v>
+        <v>1847.79144208837</v>
       </c>
       <c r="F5" t="n">
-        <v>18612.96537824157</v>
+        <v>16273.50102412695</v>
       </c>
       <c r="G5" t="n">
-        <v>45797.54891125324</v>
+        <v>45598.77910106056</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1224700924112245</v>
+        <v>0.1219385496190539</v>
       </c>
     </row>
   </sheetData>
